--- a/artfynd/A 56851-2019 artfynd.xlsx
+++ b/artfynd/A 56851-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125325902</v>
+        <v>125335997</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -708,11 +708,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337367</v>
+        <v>337366</v>
       </c>
       <c r="R2" t="n">
-        <v>6611231</v>
+        <v>6611221</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 56851-2019 artfynd.xlsx
+++ b/artfynd/A 56851-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125335997</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 56851-2019 artfynd.xlsx
+++ b/artfynd/A 56851-2019 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125335997</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
